--- a/Libraries/Vehicle/Dampers/Damper/sm_car_data_Damper_Nonlinear.xlsx
+++ b/Libraries/Vehicle/Dampers/Damper/sm_car_data_Damper_Nonlinear.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Dampers\Damper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F95476-A88C-4AC3-82C4-E88AD543326B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CA3EEF-E7AD-407D-9462-23CD05E7F45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4260" yWindow="1830" windowWidth="25575" windowHeight="13875" xr2:uid="{B9C97C16-4F33-494F-A20E-FB2F7931B984}"/>
+    <workbookView xWindow="14340" yWindow="0" windowWidth="14565" windowHeight="15585" tabRatio="669" firstSheet="1" activeTab="2" xr2:uid="{B9C97C16-4F33-494F-A20E-FB2F7931B984}"/>
   </bookViews>
   <sheets>
     <sheet name="Sedan_HambaLG_f" sheetId="1" r:id="rId1"/>
     <sheet name="Sedan_HambaLG_r" sheetId="2" r:id="rId2"/>
+    <sheet name="SUV_Landy_TA3_r" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="32">
   <si>
     <t>Units</t>
   </si>
@@ -127,6 +128,9 @@
   </si>
   <si>
     <t>Must be consistent with values in Linkage</t>
+  </si>
+  <si>
+    <t>SUV_Landy_TA3_Nonlinear_A2</t>
   </si>
 </sst>
 </file>
@@ -212,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -249,11 +253,27 @@
     <xf numFmtId="164" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -959,12 +979,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A17">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B15">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1341,7 +1361,390 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A17">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B15">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E47EE437-5E40-44A9-8CEF-7C7B3AABDB5C}">
+  <sheetPr>
+    <tabColor theme="8" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" customWidth="1"/>
+    <col min="11" max="15" width="6.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="10">
+        <v>-0.5</v>
+      </c>
+      <c r="J5" s="10">
+        <v>-0.3</v>
+      </c>
+      <c r="K5" s="10">
+        <v>-0.1</v>
+      </c>
+      <c r="L5" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="M5" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="N5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="O5" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="11">
+        <f t="shared" ref="H6:O6" si="0">H5*$J$20</f>
+        <v>-20000</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="0"/>
+        <v>-10000</v>
+      </c>
+      <c r="J6" s="11">
+        <f t="shared" si="0"/>
+        <v>-6000</v>
+      </c>
+      <c r="K6" s="11">
+        <f t="shared" si="0"/>
+        <v>-2000</v>
+      </c>
+      <c r="L6" s="11">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+      <c r="M6" s="11">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="N6" s="11">
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+      <c r="O6" s="11">
+        <f t="shared" si="0"/>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="22">
+        <v>2E-3</v>
+      </c>
+      <c r="G7" s="22">
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="H7" s="22">
+        <v>0.80200000000000005</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="22">
+        <v>-2.4E-2</v>
+      </c>
+      <c r="G8" s="22">
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="H8" s="22">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="23">
+        <f>0.3+H10</f>
+        <v>0.11499999999999999</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="23">
+        <v>-0.185</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="14">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="14">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="14">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B16" s="15"/>
+      <c r="H16" s="16"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="15"/>
+      <c r="H17" s="16"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J20" s="18">
+        <v>20000</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A4:A17">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
